--- a/Data_Product/App_Data/BM_NhatKyDungSanXuat.xlsx
+++ b/Data_Product/App_Data/BM_NhatKyDungSanXuat.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HPDQ_BICH PHUONG\PM BCSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software\ThongKePKH\DATAPRODUCT_DEV\Data_Product\App_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBD88531-BD38-4420-B98E-0C3B8A47CBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F154D86-1EEC-467C-A1AA-37A551D80962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C55D740C-D1E6-4AF1-8652-5A16423F5332}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{C55D740C-D1E6-4AF1-8652-5A16423F5332}"/>
   </bookViews>
   <sheets>
     <sheet name="BM" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BM!$A$1:$V$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BM!$A$1:$AD$17</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>TỔNG HỢP DỮ LIỆU NHẬT KÍ DỪNG SẢN XUẤT</t>
   </si>
@@ -74,18 +74,12 @@
     <t>Tổng số giờ dừng máy (Giờ)</t>
   </si>
   <si>
-    <t>Dừng máy do Thiết bị</t>
-  </si>
-  <si>
     <t>Dừng máy do Sự cố công nghệ</t>
   </si>
   <si>
     <t>Dừng máy do Chờ công nghệ</t>
   </si>
   <si>
-    <t>Dừng máy do Khách quan</t>
-  </si>
-  <si>
     <t>Nội dung dừng máy</t>
   </si>
   <si>
@@ -123,19 +117,79 @@
   </si>
   <si>
     <t>Tình trạng</t>
+  </si>
+  <si>
+    <t>Cụm thiết bị</t>
+  </si>
+  <si>
+    <t>Thiết bị Cơ điện</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Số sự cố 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(lần)</t>
+    </r>
+  </si>
+  <si>
+    <t>TG chờ xử lý sự cố
+(phút)</t>
+  </si>
+  <si>
+    <t>Thời gian xử lý SC
+(phút)</t>
+  </si>
+  <si>
+    <t>Thời gian sự cố
+(phút)</t>
+  </si>
+  <si>
+    <t>Công nghệ</t>
+  </si>
+  <si>
+    <t>TG dừng khách quan</t>
+  </si>
+  <si>
+    <t>TG chờ khác</t>
+  </si>
+  <si>
+    <t>TG dừng BTBD thực tế</t>
+  </si>
+  <si>
+    <t>TG dừng theo KH BTBD tháng (giờ)</t>
+  </si>
+  <si>
+    <t>Gây dừng dây chuyền</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -183,8 +237,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,8 +272,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -258,62 +339,152 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{258D81EB-7EC4-4551-ACBF-464C90603E26}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -517,9 +688,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -557,7 +728,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -663,7 +834,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -805,7 +976,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756BAF69-AE4A-460A-B70D-7F98F75C7929}">
-  <dimension ref="A3:V10"/>
+  <dimension ref="A3:AD10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
@@ -821,167 +992,226 @@
     <col min="3" max="3" width="5.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
-    <col min="10" max="13" width="9.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="27.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="1" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10.140625" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="7" width="17.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" customWidth="1"/>
+    <col min="10" max="17" width="13.7109375" style="1" customWidth="1"/>
+    <col min="18" max="22" width="9.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" style="1" customWidth="1"/>
+    <col min="24" max="27" width="9.7109375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="10" style="1" customWidth="1"/>
+    <col min="30" max="30" width="10.140625" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
     </row>
-    <row r="4" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
     </row>
-    <row r="5" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="I6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="K6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="Q7" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>27</v>
-      </c>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
     </row>
-    <row r="7" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
+    <row r="8" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
     </row>
-    <row r="8" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-    </row>
-    <row r="9" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -989,40 +1219,50 @@
         <v>45778</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="J9" s="8">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="17">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="H9" s="17">
-        <v>0.375</v>
-      </c>
-      <c r="I9" s="17">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
     </row>
-    <row r="10" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -1030,60 +1270,82 @@
         <v>45803</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="7"/>
+      <c r="H10" s="8">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="17">
-        <v>0.88541666666666663</v>
-      </c>
-      <c r="H10" s="17">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17">
-        <v>0.11458333333333333</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="A3:V3"/>
-    <mergeCell ref="A4:V4"/>
+  <mergeCells count="29">
+    <mergeCell ref="A3:AD3"/>
+    <mergeCell ref="A4:AD4"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:H8"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="W6:W8"/>
     <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
   </mergeCells>
   <pageMargins left="0.37" right="0.17" top="0.3" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>

--- a/Data_Product/App_Data/BM_NhatKyDungSanXuat.xlsx
+++ b/Data_Product/App_Data/BM_NhatKyDungSanXuat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software\ThongKePKH\DATAPRODUCT_DEV\Data_Product\App_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F154D86-1EEC-467C-A1AA-37A551D80962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8107244C-7AA9-4C58-9DA3-02CB536F02DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{C55D740C-D1E6-4AF1-8652-5A16423F5332}"/>
   </bookViews>
@@ -403,33 +403,24 @@
     <xf numFmtId="20" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -439,6 +430,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -448,6 +448,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -470,15 +479,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1006,108 +1006,108 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
     </row>
     <row r="4" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="15"/>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="15"/>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="15"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
     </row>
     <row r="5" spans="1:30" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="18" t="s">
         <v>13</v>
       </c>
       <c r="L6" s="21" t="s">
@@ -1120,96 +1120,96 @@
         <v>32</v>
       </c>
       <c r="Q6" s="23"/>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="10" t="s">
+      <c r="T6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="U6" s="10" t="s">
+      <c r="U6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="V6" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="W6" s="9" t="s">
+      <c r="W6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="X6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="Y6" s="9" t="s">
+      <c r="Y6" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="24" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="N7" s="24" t="s">
+      <c r="N7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="O7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="P7" s="28" t="s">
+      <c r="P7" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="30" t="s">
+      <c r="Q7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
     </row>
     <row r="8" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="26"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
     </row>
     <row r="9" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -1317,6 +1317,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
     <mergeCell ref="A3:AD3"/>
     <mergeCell ref="A4:AD4"/>
     <mergeCell ref="A6:A8"/>
@@ -1333,19 +1346,6 @@
     <mergeCell ref="G6:G8"/>
     <mergeCell ref="K6:K8"/>
     <mergeCell ref="L6:O6"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
   </mergeCells>
   <pageMargins left="0.37" right="0.17" top="0.3" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>
